--- a/WebContent/FileData/template/회원_일괄수정_서식.xlsx
+++ b/WebContent/FileData/template/회원_일괄수정_서식.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00dbm04\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\26.2.121.55\공유드라이브\시스템개발그룹\#개인폴더\공ㅇㅇ\엑셀업로드용_XLSX_파일들\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB5CBBC-4AF0-43D4-8F27-30BBEABB6E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16410" yWindow="10890" windowWidth="21465" windowHeight="12090"/>
+    <workbookView xWindow="59025" yWindow="3570" windowWidth="33465" windowHeight="16485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,29 +20,18 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>00dbm</author>
     <author>jhnam</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -166,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -383,7 +373,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -748,7 +738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -837,7 +827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -926,7 +916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1225,7 +1215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="1" shapeId="0">
+    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1311,7 +1301,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>성명</t>
   </si>
@@ -1417,13 +1407,25 @@
   </si>
   <si>
     <t>회사번호</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일수신</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMS수신</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고성정보수신</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1655,7 +1657,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1841,8 +1843,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1981,6 +1995,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2113,7 +2142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2126,51 +2155,60 @@
     <xf numFmtId="0" fontId="27" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - 강조색1 2" xfId="2"/>
-    <cellStyle name="20% - 강조색2 2" xfId="3"/>
-    <cellStyle name="20% - 강조색3 2" xfId="4"/>
-    <cellStyle name="20% - 강조색4 2" xfId="5"/>
-    <cellStyle name="20% - 강조색5 2" xfId="6"/>
-    <cellStyle name="20% - 강조색6 2" xfId="7"/>
-    <cellStyle name="40% - 강조색1 2" xfId="8"/>
-    <cellStyle name="40% - 강조색2 2" xfId="9"/>
-    <cellStyle name="40% - 강조색3 2" xfId="10"/>
-    <cellStyle name="40% - 강조색4 2" xfId="11"/>
-    <cellStyle name="40% - 강조색5 2" xfId="12"/>
-    <cellStyle name="40% - 강조색6 2" xfId="13"/>
-    <cellStyle name="60% - 강조색1 2" xfId="14"/>
-    <cellStyle name="60% - 강조색2 2" xfId="15"/>
-    <cellStyle name="60% - 강조색3 2" xfId="16"/>
-    <cellStyle name="60% - 강조색4 2" xfId="17"/>
-    <cellStyle name="60% - 강조색5 2" xfId="18"/>
-    <cellStyle name="60% - 강조색6 2" xfId="19"/>
-    <cellStyle name="강조색1 2" xfId="20"/>
-    <cellStyle name="강조색2 2" xfId="21"/>
-    <cellStyle name="강조색3 2" xfId="22"/>
-    <cellStyle name="강조색4 2" xfId="23"/>
-    <cellStyle name="강조색5 2" xfId="24"/>
-    <cellStyle name="강조색6 2" xfId="25"/>
-    <cellStyle name="경고문 2" xfId="26"/>
-    <cellStyle name="계산 2" xfId="27"/>
-    <cellStyle name="나쁨 2" xfId="28"/>
-    <cellStyle name="메모 2" xfId="29"/>
-    <cellStyle name="보통 2" xfId="30"/>
-    <cellStyle name="설명 텍스트 2" xfId="31"/>
-    <cellStyle name="셀 확인 2" xfId="32"/>
-    <cellStyle name="연결된 셀 2" xfId="33"/>
-    <cellStyle name="요약 2" xfId="34"/>
-    <cellStyle name="입력 2" xfId="35"/>
-    <cellStyle name="제목 1 2" xfId="37"/>
-    <cellStyle name="제목 2 2" xfId="38"/>
-    <cellStyle name="제목 3 2" xfId="39"/>
-    <cellStyle name="제목 4 2" xfId="40"/>
-    <cellStyle name="제목 5" xfId="36"/>
-    <cellStyle name="좋음 2" xfId="41"/>
-    <cellStyle name="출력 2" xfId="42"/>
+    <cellStyle name="20% - 강조색1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - 강조색2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - 강조색3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - 강조색4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - 강조색5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - 강조색6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - 강조색1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - 강조색2 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - 강조색3 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - 강조색4 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - 강조색5 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - 강조색6 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - 강조색1 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - 강조색2 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - 강조색3 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - 강조색4 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - 강조색5 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - 강조색6 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="강조색1 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="강조색2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="강조색3 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="강조색4 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="강조색5 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="강조색6 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="경고문 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="계산 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="나쁨 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="메모 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="보통 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="설명 텍스트 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="셀 확인 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="연결된 셀 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="요약 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="입력 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="제목 1 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="제목 2 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="제목 3 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="제목 4 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="제목 5" xfId="36" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="좋음 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="출력 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2501,9 +2539,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AI1"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="8.25" bestFit="1" customWidth="1"/>
@@ -2531,9 +2569,10 @@
     <col min="30" max="30" width="11.75" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="9.875" customWidth="1"/>
     <col min="32" max="32" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.0625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2558,77 +2597,86 @@
       <c r="H1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>25</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
